--- a/config/yunying/limitbuygift.xlsx
+++ b/config/yunying/limitbuygift.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="limitbuygift" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="limitbuygift" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1396,7 +1396,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>23001</t>
@@ -1432,7 +1431,6 @@
           <t>{11=3;13=1;gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>2001</t>
@@ -1443,9 +1441,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
@@ -1456,10 +1451,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -1472,7 +1463,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>23001</t>
@@ -1508,7 +1498,6 @@
           <t>{11=3;13=1;gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>2002</t>
@@ -1519,9 +1508,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
@@ -1532,10 +1518,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -1548,7 +1530,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>23001</t>
@@ -1584,7 +1565,6 @@
           <t>{12=3}</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>2003</t>
@@ -1595,9 +1575,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
@@ -1608,10 +1585,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -1624,7 +1597,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>23001</t>
@@ -1660,7 +1632,6 @@
           <t>{gold=300000;rmb=5000}</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>2004</t>
@@ -1671,9 +1642,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
           <t>1</t>
@@ -1684,10 +1652,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -1700,7 +1664,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>23001</t>
@@ -1736,7 +1699,6 @@
           <t>{12=3;13=1;gold=300000;11=1}</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>2005</t>
@@ -1747,9 +1709,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
           <t>2</t>
@@ -1760,10 +1719,6 @@
           <t>10101</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -1776,7 +1731,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>23001</t>
@@ -1812,7 +1766,6 @@
           <t>{gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>2006</t>
@@ -1823,9 +1776,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
           <t>3</t>
@@ -1841,9 +1791,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_sstp.png</t>
@@ -1856,7 +1803,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>23001</t>
@@ -1892,7 +1838,6 @@
           <t>{gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>2007</t>
@@ -1903,19 +1848,11 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -1928,7 +1865,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>23001</t>
@@ -1964,7 +1900,6 @@
           <t>{gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>2007</t>
@@ -1975,9 +1910,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
           <t>4</t>
@@ -1988,10 +1920,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -2004,7 +1932,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>23001</t>
@@ -2040,7 +1967,6 @@
           <t>{gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>2007</t>
@@ -2051,9 +1977,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
           <t>5</t>
@@ -2064,10 +1987,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -2080,7 +1999,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>23001</t>
@@ -2116,7 +2034,6 @@
           <t>{gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>2007</t>
@@ -2127,9 +2044,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>6</t>
@@ -2172,7 +2086,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>23001</t>
@@ -2208,7 +2121,6 @@
           <t>{gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>2007</t>
@@ -2219,9 +2131,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
           <t>6</t>
@@ -2237,9 +2146,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -2252,7 +2158,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>23001</t>
@@ -2288,7 +2193,6 @@
           <t>{gold=300000;rmb=5000;12=5}</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>2007</t>
@@ -2299,9 +2203,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
           <t>5</t>
@@ -2312,7 +2213,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>3</t>
@@ -2339,28 +2239,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -2379,7 +2258,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Lv10パック</t>
+          <t>Lv10包</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2402,7 +2281,6 @@
           <t>{card={id=21};rmb=12}</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>101</t>
@@ -2413,9 +2291,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
           <t>1</t>
@@ -2426,10 +2301,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -2459,7 +2330,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Lv20パック</t>
+          <t>Lv20包</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2482,7 +2353,6 @@
           <t>{card={id=21};rmb=12}</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>102</t>
@@ -2493,9 +2363,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
           <t>1</t>
@@ -2506,10 +2373,6 @@
           <t>20</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -2539,7 +2402,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Lv30パック</t>
+          <t>Lv30包</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2562,7 +2425,6 @@
           <t>{card={id=21};rmb=12}</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>103</t>
@@ -2573,9 +2435,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
           <t>1</t>
@@ -2586,10 +2445,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -2619,7 +2474,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>Lv40パック</t>
+          <t>Lv40包</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2642,7 +2497,6 @@
           <t>{card={id=21};rmb=12}</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>104</t>
@@ -2653,9 +2507,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>1</t>
@@ -2666,10 +2517,6 @@
           <t>40</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -2699,7 +2546,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>ステージパック</t>
+          <t>关卡包</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2722,7 +2569,6 @@
           <t>{card={id=21};rmb=12}</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>105</t>
@@ -2733,9 +2579,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>2</t>
@@ -2746,10 +2589,6 @@
           <t>10101</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -2779,7 +2618,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>突破パック</t>
+          <t>突破包</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2802,7 +2641,6 @@
           <t>{card={id=21};rmb=12}</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>106</t>
@@ -2813,9 +2651,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>3</t>
@@ -2831,9 +2666,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_sstp.png</t>
@@ -2863,7 +2695,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>解放パック</t>
+          <t>解放包</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2886,7 +2718,6 @@
           <t>{card={id=21};rmb=12}</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>107</t>
@@ -2897,19 +2728,11 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -2939,7 +2762,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>初回パック</t>
+          <t>初回包装</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2962,7 +2785,6 @@
           <t>{12=3}</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>108</t>
@@ -2973,9 +2795,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
           <t>4</t>
@@ -2986,10 +2805,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -3019,7 +2834,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>VIP15パック</t>
+          <t>VIP15包</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3042,7 +2857,6 @@
           <t>{12=3}</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>109</t>
@@ -3053,9 +2867,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
           <t>5</t>
@@ -3066,10 +2877,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -3099,7 +2906,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>レアパックS</t>
+          <t>稀有背包S</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3122,7 +2929,6 @@
           <t>{12=3}</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>110</t>
@@ -3133,9 +2939,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
           <t>6</t>
@@ -3195,7 +2998,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>レアパックB</t>
+          <t>稀土B</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3218,7 +3021,6 @@
           <t>{12=3}</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>111</t>
@@ -3229,9 +3031,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>6</t>
@@ -3247,9 +3046,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -3279,7 +3075,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>VIPパック</t>
+          <t>VIP包</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3302,7 +3098,6 @@
           <t>{12=3}</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>112</t>
@@ -3313,9 +3108,6 @@
           <t>120</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>5</t>
@@ -3326,7 +3118,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>3</t>
@@ -3353,28 +3144,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
@@ -3393,7 +3163,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>限定パック</t>
+          <t>限量包装</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3416,7 +3186,6 @@
           <t>{rmb=600;503=10;452=100}</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>106</t>
@@ -3427,7 +3196,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>1</t>
@@ -3448,10 +3216,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -3481,7 +3245,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>限定パック</t>
+          <t>限量包装</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3504,7 +3268,6 @@
           <t>{rmb=600;503=10;452=100}</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>106</t>
@@ -3515,7 +3278,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>2</t>
@@ -3536,10 +3298,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -3569,7 +3327,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>限定パック</t>
+          <t>限量包装</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3592,7 +3350,6 @@
           <t>{rmb=600;503=10;452=100}</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>106</t>
@@ -3603,7 +3360,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
           <t>3</t>
@@ -3624,10 +3380,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -3657,7 +3409,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>限定パック</t>
+          <t>限量包装</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3680,7 +3432,6 @@
           <t>{rmb=600;503=10;452=100}</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>106</t>
@@ -3691,7 +3442,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
           <t>4</t>
@@ -3712,10 +3462,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
       <c r="U33" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -3745,7 +3491,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>限定パック</t>
+          <t>限量包装</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3768,7 +3514,6 @@
           <t>{rmb=600;503=10;452=100}</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>106</t>
@@ -3779,7 +3524,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>5</t>
@@ -3800,10 +3544,6 @@
           <t>80</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -3833,7 +3573,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>限定パック</t>
+          <t>限量包装</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3856,7 +3596,6 @@
           <t>{rmb=600;503=10;452=100}</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>106</t>
@@ -3867,7 +3606,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
           <t>6</t>
@@ -3888,10 +3626,6 @@
           <t>90</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -3921,7 +3655,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>限定パック</t>
+          <t>限量包装</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3944,7 +3678,6 @@
           <t>{rmb=600;503=10;452=100}</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>106</t>
@@ -3955,7 +3688,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
           <t>7</t>
@@ -3976,10 +3708,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -3991,28 +3719,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
@@ -4031,7 +3738,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>豪華パック</t>
+          <t>豪华包</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4054,7 +3761,6 @@
           <t>{card={id=741};rmb=3280;519=10;942=1}</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>112</t>
@@ -4065,7 +3771,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>1</t>
@@ -4086,10 +3791,6 @@
           <t>30</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -4119,7 +3820,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>豪華パック</t>
+          <t>豪华包</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4142,7 +3843,6 @@
           <t>{card={id=741};rmb=3280;519=10;942=1}</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>112</t>
@@ -4153,7 +3853,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
           <t>2</t>
@@ -4174,10 +3873,6 @@
           <t>50</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -4207,7 +3902,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>豪華パック</t>
+          <t>豪华包</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4230,7 +3925,6 @@
           <t>{card={id=741};rmb=3280;519=10;942=1}</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>112</t>
@@ -4241,7 +3935,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
           <t>3</t>
@@ -4262,10 +3955,6 @@
           <t>60</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -4295,7 +3984,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>豪華パック</t>
+          <t>豪华包</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4318,7 +4007,6 @@
           <t>{card={id=741};rmb=3280;519=10;942=1}</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>112</t>
@@ -4329,7 +4017,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>4</t>
@@ -4350,10 +4037,6 @@
           <t>70</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
       <c r="U41" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -4383,7 +4066,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>豪華パック</t>
+          <t>豪华包</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -4406,7 +4089,6 @@
           <t>{card={id=741};rmb=3280;519=10;942=1}</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>112</t>
@@ -4417,7 +4099,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
           <t>5</t>
@@ -4438,10 +4119,6 @@
           <t>80</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -4471,7 +4148,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>豪華パック</t>
+          <t>豪华包</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4494,7 +4171,6 @@
           <t>{card={id=741};rmb=3280;519=10;942=1}</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>112</t>
@@ -4505,7 +4181,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
           <t>6</t>
@@ -4526,10 +4201,6 @@
           <t>90</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -4559,7 +4230,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>豪華パック</t>
+          <t>豪华包</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4582,7 +4253,6 @@
           <t>{card={id=741};rmb=3280;519=10;942=1}</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>112</t>
@@ -4593,7 +4263,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
           <t>7</t>
@@ -4614,10 +4283,6 @@
           <t>100</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -4629,28 +4294,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-    </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
@@ -4669,7 +4313,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>限定パック</t>
+          <t>限量包装</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4692,7 +4336,6 @@
           <t>{rmb=980;6211=1;602=30;gold=300000}</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>108</t>
@@ -4703,9 +4346,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
           <t>4</t>
@@ -4716,10 +4356,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_tgzl.png</t>
@@ -4731,28 +4367,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-    </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -4771,7 +4386,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4794,7 +4409,6 @@
           <t>{rmb=6480;521=80;gold=1000000}</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>113</t>
@@ -4805,9 +4419,6 @@
           <t>240</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>6</t>
@@ -4823,9 +4434,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_sstp.png</t>
@@ -4837,28 +4445,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-    </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -4877,7 +4464,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4900,7 +4487,6 @@
           <t>{rmb=120;stamina=100;503=1}</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>102</t>
@@ -4911,7 +4497,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>1</t>
@@ -4920,10 +4505,6 @@
       <c r="P50" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -4953,7 +4534,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4976,7 +4557,6 @@
           <t>{rmb=980;503=20;501=2}</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>108</t>
@@ -4987,7 +4567,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
       <c r="O51" t="inlineStr">
         <is>
           <t>1</t>
@@ -4996,14 +4575,12 @@
       <c r="P51" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="n">
         <v>5</v>
       </c>
       <c r="S51" t="n">
         <v>2</v>
       </c>
-      <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5033,7 +4610,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5056,7 +4633,6 @@
           <t>{503=20;941=1}</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>108</t>
@@ -5067,7 +4643,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="O52" t="inlineStr">
         <is>
           <t>1</t>
@@ -5076,14 +4651,12 @@
       <c r="P52" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="n">
         <v>5</v>
       </c>
       <c r="S52" t="n">
         <v>2</v>
       </c>
-      <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5113,7 +4686,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5136,7 +4709,6 @@
           <t>{rmb=1680;503=20;501=1}</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
           <t>108</t>
@@ -5147,7 +4719,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
       <c r="O53" t="inlineStr">
         <is>
           <t>1</t>
@@ -5156,10 +4727,6 @@
       <c r="P53" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5189,7 +4756,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5212,7 +4779,6 @@
           <t>{503=40;2103=30;rmb=500}</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>108</t>
@@ -5223,7 +4789,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="O54" t="inlineStr">
         <is>
           <t>1</t>
@@ -5232,14 +4797,12 @@
       <c r="P54" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="n">
         <v>5</v>
       </c>
       <c r="S54" t="n">
         <v>2</v>
       </c>
-      <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5269,7 +4832,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5292,7 +4855,6 @@
           <t>{rmb=1980;6059=2;501=3}</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
           <t>111</t>
@@ -5303,7 +4865,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr"/>
       <c r="O55" t="inlineStr">
         <is>
           <t>1</t>
@@ -5312,14 +4873,12 @@
       <c r="P55" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="n">
         <v>5</v>
       </c>
       <c r="S55" t="n">
         <v>2</v>
       </c>
-      <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5349,7 +4908,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5372,7 +4931,6 @@
           <t>{rmb=1980;6059=2;501=5}</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
           <t>111</t>
@@ -5383,7 +4941,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr"/>
       <c r="O56" t="inlineStr">
         <is>
           <t>1</t>
@@ -5392,10 +4949,6 @@
       <c r="P56" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5425,7 +4978,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5448,7 +5001,6 @@
           <t>{rmb=1980;6059=1;501=5}</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr">
         <is>
           <t>111</t>
@@ -5459,7 +5011,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr"/>
       <c r="O57" t="inlineStr">
         <is>
           <t>1</t>
@@ -5468,14 +5019,12 @@
       <c r="P57" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="n">
         <v>5</v>
       </c>
       <c r="S57" t="n">
         <v>2</v>
       </c>
-      <c r="T57" t="inlineStr"/>
       <c r="U57" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5505,7 +5054,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5528,7 +5077,6 @@
           <t>{rmb=1980;6059=1;501=8}</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr">
         <is>
           <t>111</t>
@@ -5539,7 +5087,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr"/>
       <c r="O58" t="inlineStr">
         <is>
           <t>1</t>
@@ -5554,7 +5101,6 @@
       <c r="S58" t="n">
         <v>3</v>
       </c>
-      <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5584,7 +5130,7 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5607,7 +5153,6 @@
           <t>{rmb=3980;6059=2;501=5}</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr">
         <is>
           <t>112</t>
@@ -5618,7 +5163,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr"/>
       <c r="O59" t="inlineStr">
         <is>
           <t>1</t>
@@ -5633,7 +5177,6 @@
       <c r="S59" t="n">
         <v>3</v>
       </c>
-      <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5663,7 +5206,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5686,7 +5229,6 @@
           <t>{rmb=6480;6059=3;501=10}</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
           <t>113</t>
@@ -5697,7 +5239,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>1</t>
@@ -5712,7 +5253,6 @@
       <c r="S60" t="n">
         <v>4</v>
       </c>
-      <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5742,7 +5282,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5765,7 +5305,6 @@
           <t>{rmb=6480;6059=4;501=6}</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
           <t>113</t>
@@ -5776,7 +5315,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>1</t>
@@ -5791,7 +5329,6 @@
       <c r="S61" t="n">
         <v>4</v>
       </c>
-      <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5821,7 +5358,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>装飾パック</t>
+          <t>装饰包</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5844,7 +5381,6 @@
           <t>{rmb=6480;526=90;6059=2;501=6}</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr">
         <is>
           <t>113</t>
@@ -5855,7 +5391,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr"/>
       <c r="O62" t="inlineStr">
         <is>
           <t>1</t>
@@ -5864,10 +5399,6 @@
       <c r="P62" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -5880,7 +5411,6 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>20011</t>
@@ -5896,15 +5426,11 @@
           <t>装飾パック</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
       <c r="H63" s="3" t="inlineStr">
         <is>
           <t>{503=100;942=2;rmb=2000}</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
           <t>113</t>
@@ -5915,7 +5441,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
         <is>
           <t>1</t>
@@ -5924,12 +5449,6 @@
       <c r="P63" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="B64" s="2" t="n"/>
@@ -5954,7 +5473,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>刻印パック</t>
+          <t>刻字包</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5977,7 +5496,6 @@
           <t>{rmb=980;111=400;112=80}</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
           <t>108</t>
@@ -5988,7 +5506,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
       <c r="O65" t="inlineStr">
         <is>
           <t>1</t>
@@ -5997,10 +5514,6 @@
       <c r="P65" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
       <c r="U65" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6030,7 +5543,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>刻印パック</t>
+          <t>刻字包</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6053,7 +5566,6 @@
           <t>{rmb=1980;111=800;112=150}</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
           <t>111</t>
@@ -6064,7 +5576,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
       <c r="O66" t="inlineStr">
         <is>
           <t>1</t>
@@ -6073,10 +5584,6 @@
       <c r="P66" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
       <c r="U66" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6106,7 +5613,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>刻印パック</t>
+          <t>刻字包</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6129,7 +5636,6 @@
           <t>{rmb=1980;111=800;112=160}</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr">
         <is>
           <t>111</t>
@@ -6140,7 +5646,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
       <c r="O67" t="inlineStr">
         <is>
           <t>1</t>
@@ -6149,10 +5654,6 @@
       <c r="P67" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
       <c r="U67" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6182,7 +5683,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>刻印パック</t>
+          <t>刻字包</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6205,7 +5706,6 @@
           <t>{rmb=3280;111=1600;112=320}</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr">
         <is>
           <t>112</t>
@@ -6216,7 +5716,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
       <c r="O68" t="inlineStr">
         <is>
           <t>1</t>
@@ -6225,10 +5724,6 @@
       <c r="P68" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
       <c r="U68" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6262,7 +5757,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -6285,7 +5780,6 @@
           <t>{503=2;941=1;rmb=120}</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
         <v>102</v>
       </c>
@@ -6294,7 +5788,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="O70" t="inlineStr">
         <is>
           <t>1</t>
@@ -6303,10 +5796,6 @@
       <c r="P70" t="n">
         <v>11</v>
       </c>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
       <c r="U70" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6336,7 +5825,7 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6359,7 +5848,6 @@
           <t>{503=10;941=2;rmb=200}</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
       <c r="J71" t="n">
         <v>106</v>
       </c>
@@ -6368,7 +5856,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
           <t>1</t>
@@ -6377,10 +5864,6 @@
       <c r="P71" t="n">
         <v>11</v>
       </c>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
       <c r="U71" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6410,7 +5893,7 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6433,7 +5916,6 @@
           <t>{rmb=300;2103=10;gold=100000}</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
       <c r="J72" t="n">
         <v>106</v>
       </c>
@@ -6442,7 +5924,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
           <t>1</t>
@@ -6451,14 +5932,12 @@
       <c r="P72" t="n">
         <v>11</v>
       </c>
-      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="n">
         <v>5</v>
       </c>
       <c r="S72" t="n">
         <v>2</v>
       </c>
-      <c r="T72" t="inlineStr"/>
       <c r="U72" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6488,7 +5967,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6511,7 +5990,6 @@
           <t>{rmb=300;2103=20;gold=200000}</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
       <c r="J73" t="n">
         <v>106</v>
       </c>
@@ -6520,7 +5998,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
           <t>1</t>
@@ -6529,14 +6006,12 @@
       <c r="P73" t="n">
         <v>11</v>
       </c>
-      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="n">
         <v>5</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
       </c>
-      <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6566,7 +6041,7 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6589,7 +6064,6 @@
           <t>{503=20;941=1}</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr">
         <is>
           <t>108</t>
@@ -6600,7 +6074,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
           <t>1</t>
@@ -6609,14 +6082,12 @@
       <c r="P74" t="n">
         <v>11</v>
       </c>
-      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="n">
         <v>5</v>
       </c>
       <c r="S74" t="n">
         <v>2</v>
       </c>
-      <c r="T74" t="inlineStr"/>
       <c r="U74" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6646,7 +6117,7 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -6669,7 +6140,6 @@
           <t>{rmb=980;942=1;gold=500000}</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr">
         <is>
           <t>108</t>
@@ -6680,7 +6150,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
           <t>1</t>
@@ -6689,10 +6158,6 @@
       <c r="P75" t="n">
         <v>11</v>
       </c>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6722,7 +6187,7 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -6745,7 +6210,6 @@
           <t>{rmb=980;2103=80;gold=800000}</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr">
         <is>
           <t>108</t>
@@ -6756,7 +6220,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
       <c r="O76" t="inlineStr">
         <is>
           <t>1</t>
@@ -6765,14 +6228,12 @@
       <c r="P76" t="n">
         <v>11</v>
       </c>
-      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="n">
         <v>5</v>
       </c>
       <c r="S76" t="n">
         <v>2</v>
       </c>
-      <c r="T76" t="inlineStr"/>
       <c r="U76" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6802,7 +6263,7 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -6825,7 +6286,6 @@
           <t>{rmb=2680;942=1;gold=500000}</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
       <c r="J77" t="inlineStr">
         <is>
           <t>111</t>
@@ -6836,7 +6296,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
       <c r="O77" t="inlineStr">
         <is>
           <t>1</t>
@@ -6845,14 +6304,12 @@
       <c r="P77" t="n">
         <v>11</v>
       </c>
-      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="n">
         <v>5</v>
       </c>
       <c r="S77" t="n">
         <v>3</v>
       </c>
-      <c r="T77" t="inlineStr"/>
       <c r="U77" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6882,7 +6339,7 @@
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6905,7 +6362,6 @@
           <t>{rmb=1980;2103=160;gold=1600000}</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr">
         <is>
           <t>111</t>
@@ -6916,7 +6372,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L78" t="inlineStr"/>
       <c r="O78" t="inlineStr">
         <is>
           <t>1</t>
@@ -6925,10 +6380,6 @@
       <c r="P78" t="n">
         <v>11</v>
       </c>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -6941,7 +6392,6 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>20011</t>
@@ -6957,32 +6407,19 @@
           <t>装備パック</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr"/>
       <c r="H79" s="3" t="inlineStr">
         <is>
           <t>{rmb=3280;2103=240;gold=2400000}</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="n">
         <v>11</v>
       </c>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7002,7 +6439,7 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7025,7 +6462,6 @@
           <t>{942=1;rmb=2000;13=20}</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr">
         <is>
           <t>112</t>
@@ -7036,7 +6472,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L80" t="inlineStr"/>
       <c r="O80" t="inlineStr">
         <is>
           <t>1</t>
@@ -7051,7 +6486,6 @@
       <c r="S80" t="n">
         <v>4</v>
       </c>
-      <c r="T80" t="inlineStr"/>
       <c r="U80" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7081,7 +6515,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7104,7 +6538,6 @@
           <t>{rmb=2280;942=1;gold=100000}</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr">
         <is>
           <t>112</t>
@@ -7115,7 +6548,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
           <t>1</t>
@@ -7130,7 +6562,6 @@
       <c r="S81" t="n">
         <v>4</v>
       </c>
-      <c r="T81" t="inlineStr"/>
       <c r="U81" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7160,7 +6591,7 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7183,7 +6614,6 @@
           <t>{rmb=3280;942=1;2103=60}</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr">
         <is>
           <t>112</t>
@@ -7194,7 +6624,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="O82" t="inlineStr">
         <is>
           <t>1</t>
@@ -7203,9 +6632,6 @@
       <c r="P82" t="n">
         <v>11</v>
       </c>
-      <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
       <c r="U82" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7235,7 +6661,7 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7258,7 +6684,6 @@
           <t>{503=40;2103=30;rmb=500}</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr">
         <is>
           <t>112</t>
@@ -7269,7 +6694,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L83" t="inlineStr"/>
       <c r="O83" t="inlineStr">
         <is>
           <t>1</t>
@@ -7278,9 +6702,6 @@
       <c r="P83" t="n">
         <v>11</v>
       </c>
-      <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
       <c r="U83" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7310,7 +6731,7 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7333,7 +6754,6 @@
           <t>{rmb=5000;942=1;2103=50;gold=100000}</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
           <t>113</t>
@@ -7344,7 +6764,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L84" t="inlineStr"/>
       <c r="O84" t="inlineStr">
         <is>
           <t>1</t>
@@ -7359,7 +6778,6 @@
       <c r="S84" t="n">
         <v>4</v>
       </c>
-      <c r="T84" t="inlineStr"/>
       <c r="U84" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7389,7 +6807,7 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -7412,7 +6830,6 @@
           <t>{503=100;942=2;rmb=2000}</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr">
         <is>
           <t>113</t>
@@ -7423,7 +6840,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr"/>
       <c r="O85" t="inlineStr">
         <is>
           <t>1</t>
@@ -7432,10 +6848,6 @@
       <c r="P85" t="n">
         <v>11</v>
       </c>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
       <c r="U85" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7465,7 +6877,7 @@
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>装備パック</t>
+          <t>装备包</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7488,7 +6900,6 @@
           <t>{rmb=980;942=1;gold=500000}</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr">
         <is>
           <t>111</t>
@@ -7499,7 +6910,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr"/>
       <c r="O86" t="inlineStr">
         <is>
           <t>1</t>
@@ -7508,10 +6918,6 @@
       <c r="P86" t="n">
         <v>11</v>
       </c>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
       <c r="U86" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7545,7 +6951,7 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>強化パック</t>
+          <t>强化包</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7568,7 +6974,6 @@
           <t>{452=20;451=50;2103=5}</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
         <v>102</v>
       </c>
@@ -7577,7 +6982,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
       <c r="O88" t="inlineStr">
         <is>
           <t>1</t>
@@ -7586,10 +6990,6 @@
       <c r="P88" t="n">
         <v>24</v>
       </c>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
       <c r="U88" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7619,7 +7019,7 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>強化パック</t>
+          <t>强化包</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -7642,7 +7042,6 @@
           <t>{452=30;451=100}</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
         <v>106</v>
       </c>
@@ -7651,7 +7050,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr"/>
       <c r="O89" t="inlineStr">
         <is>
           <t>1</t>
@@ -7660,10 +7058,6 @@
       <c r="P89" t="n">
         <v>24</v>
       </c>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
       <c r="U89" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7693,7 +7087,7 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>強化パック</t>
+          <t>强化包</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7716,7 +7110,6 @@
           <t>{rmb=300;452=30;13=20}</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
         <v>106</v>
       </c>
@@ -7725,7 +7118,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr"/>
       <c r="O90" t="inlineStr">
         <is>
           <t>1</t>
@@ -7734,14 +7126,12 @@
       <c r="P90" t="n">
         <v>24</v>
       </c>
-      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="n">
         <v>5</v>
       </c>
       <c r="S90" t="n">
         <v>2</v>
       </c>
-      <c r="T90" t="inlineStr"/>
       <c r="U90" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7771,7 +7161,7 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>強化パック</t>
+          <t>强化包</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -7794,7 +7184,6 @@
           <t>{rmb=300;452=50;451=100}</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
         <v>107</v>
       </c>
@@ -7803,7 +7192,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
       <c r="O91" t="inlineStr">
         <is>
           <t>1</t>
@@ -7812,14 +7200,12 @@
       <c r="P91" t="n">
         <v>24</v>
       </c>
-      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="n">
         <v>5</v>
       </c>
       <c r="S91" t="n">
         <v>2</v>
       </c>
-      <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7849,7 +7235,7 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>強化パック</t>
+          <t>强化包</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -7872,7 +7258,6 @@
           <t>{rmb=600;452=100;451=200}</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
         <v>107</v>
       </c>
@@ -7881,7 +7266,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
       <c r="O92" t="inlineStr">
         <is>
           <t>1</t>
@@ -7890,14 +7274,12 @@
       <c r="P92" t="n">
         <v>24</v>
       </c>
-      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="n">
         <v>5</v>
       </c>
       <c r="S92" t="n">
         <v>2</v>
       </c>
-      <c r="T92" t="inlineStr"/>
       <c r="U92" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7927,7 +7309,7 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>強化パック</t>
+          <t>强化包</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -7950,7 +7332,6 @@
           <t>{rmb=980;452=200;451=400}</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
         <v>108</v>
       </c>
@@ -7959,7 +7340,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
       <c r="O93" t="inlineStr">
         <is>
           <t>1</t>
@@ -7968,10 +7348,6 @@
       <c r="P93" t="n">
         <v>24</v>
       </c>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
       <c r="U93" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -7984,7 +7360,6 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
       <c r="B94" s="2" t="inlineStr">
         <is>
           <t>20011</t>
@@ -8000,15 +7375,11 @@
           <t>強化パック</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr"/>
       <c r="H94" s="3" t="inlineStr">
         <is>
           <t>{rmb=1980;452=500;451=800}</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
         <v>111</v>
       </c>
@@ -8017,21 +7388,18 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr"/>
       <c r="O94" t="n">
         <v>1</v>
       </c>
       <c r="P94" t="n">
         <v>24</v>
       </c>
-      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="n">
         <v>5</v>
       </c>
       <c r="S94" t="n">
         <v>4</v>
       </c>
-      <c r="T94" t="inlineStr"/>
       <c r="U94" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8061,7 +7429,7 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>強化パック</t>
+          <t>强化包</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8084,7 +7452,6 @@
           <t>{rmb=3280;452=60;451=1200}</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
         <v>112</v>
       </c>
@@ -8093,7 +7460,6 @@
           <t>360</t>
         </is>
       </c>
-      <c r="L95" t="inlineStr"/>
       <c r="O95" t="n">
         <v>1</v>
       </c>
@@ -8106,7 +7472,6 @@
       <c r="S95" t="n">
         <v>4</v>
       </c>
-      <c r="T95" t="inlineStr"/>
       <c r="U95" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8140,7 +7505,7 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8171,18 +7536,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="O97" t="n">
         <v>1</v>
       </c>
       <c r="P97" t="n">
         <v>25</v>
       </c>
-      <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
       <c r="U97" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8212,7 +7571,7 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8235,7 +7594,6 @@
           <t>{rmb=60;601=10;901=20}</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
       <c r="J98" t="n">
         <v>102</v>
       </c>
@@ -8244,9 +7602,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
       <c r="O98" t="n">
         <v>1</v>
       </c>
@@ -8259,7 +7614,6 @@
       <c r="S98" t="n">
         <v>2</v>
       </c>
-      <c r="T98" t="inlineStr"/>
       <c r="U98" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8289,7 +7643,7 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8312,7 +7666,6 @@
           <t>{rmb=60;601=15;901=10}</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
       <c r="J99" t="n">
         <v>102</v>
       </c>
@@ -8321,18 +7674,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="O99" t="n">
         <v>1</v>
       </c>
       <c r="P99" t="n">
         <v>25</v>
       </c>
-      <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
       <c r="U99" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8362,7 +7709,7 @@
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8385,7 +7732,6 @@
           <t>{rmb=300;605=10;902=20}</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
       <c r="J100" t="n">
         <v>106</v>
       </c>
@@ -8394,18 +7740,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="O100" t="n">
         <v>1</v>
       </c>
       <c r="P100" t="n">
         <v>25</v>
       </c>
-      <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
       <c r="U100" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8435,7 +7775,7 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8458,7 +7798,6 @@
           <t>{rmb=980;605=30;902=80}</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
         <v>108</v>
       </c>
@@ -8467,18 +7806,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
         <v>1</v>
       </c>
       <c r="P101" t="n">
         <v>25</v>
       </c>
-      <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
       <c r="U101" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8508,7 +7841,7 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8531,7 +7864,6 @@
           <t>{rmb=1980;605=60;902=160}</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>111</t>
@@ -8542,9 +7874,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
         <v>1</v>
       </c>
@@ -8557,7 +7886,6 @@
       <c r="S102" t="n">
         <v>3</v>
       </c>
-      <c r="T102" t="inlineStr"/>
       <c r="U102" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8587,7 +7915,7 @@
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8610,7 +7938,6 @@
           <t>{rmb=3280;605=90;902=240}</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>112</t>
@@ -8621,9 +7948,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
         <v>1</v>
       </c>
@@ -8636,7 +7960,6 @@
       <c r="S103" t="n">
         <v>3</v>
       </c>
-      <c r="T103" t="inlineStr"/>
       <c r="U103" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8666,7 +7989,7 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8689,7 +8012,6 @@
           <t>{rmb=6480;605=180;902=360}</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr">
         <is>
           <t>113</t>
@@ -8700,9 +8022,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
         <v>1</v>
       </c>
@@ -8715,7 +8034,6 @@
       <c r="S104" t="n">
         <v>4</v>
       </c>
-      <c r="T104" t="inlineStr"/>
       <c r="U104" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8745,7 +8063,7 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>好感度パック</t>
+          <t>好感度面膜</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8768,7 +8086,6 @@
           <t>{rmb=6480;605=150;902=500}</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr">
         <is>
           <t>113</t>
@@ -8779,18 +8096,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
         <v>1</v>
       </c>
       <c r="P105" t="n">
         <v>25</v>
       </c>
-      <c r="R105" t="inlineStr"/>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
       <c r="U105" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8824,7 +8135,7 @@
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>探査機パック</t>
+          <t>探测器包</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8855,18 +8166,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
         <v>1</v>
       </c>
       <c r="P107" t="n">
         <v>33</v>
       </c>
-      <c r="R107" t="inlineStr"/>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
       <c r="U107" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8896,7 +8201,7 @@
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>探査機パック</t>
+          <t>探测器包</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8919,7 +8224,6 @@
           <t>{520=1;4000=30;rmb=120}</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
       <c r="J108" t="n">
         <v>102</v>
       </c>
@@ -8928,18 +8232,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="O108" t="n">
         <v>1</v>
       </c>
       <c r="P108" t="n">
         <v>33</v>
       </c>
-      <c r="R108" t="inlineStr"/>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
       <c r="U108" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -8969,7 +8267,7 @@
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>探査機パック</t>
+          <t>探测器包</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8992,7 +8290,6 @@
           <t>{520=5;962=1;rmb=200}</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
       <c r="J109" t="n">
         <v>106</v>
       </c>
@@ -9001,18 +8298,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
       <c r="O109" t="n">
         <v>1</v>
       </c>
       <c r="P109" t="n">
         <v>33</v>
       </c>
-      <c r="R109" t="inlineStr"/>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
       <c r="U109" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9042,7 +8333,7 @@
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>探査機パック</t>
+          <t>探测器包</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -9065,7 +8356,6 @@
           <t>{520=15;4000=100}</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
         <v>108</v>
       </c>
@@ -9074,9 +8364,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
         <v>1</v>
       </c>
@@ -9089,7 +8376,6 @@
       <c r="S110" t="n">
         <v>2</v>
       </c>
-      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9119,7 +8405,7 @@
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>探査機パック</t>
+          <t>探测器包</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -9142,7 +8428,6 @@
           <t>{rmb=980;520=10;4000=100}</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr"/>
       <c r="J111" t="n">
         <v>108</v>
       </c>
@@ -9151,18 +8436,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
         <v>1</v>
       </c>
       <c r="P111" t="n">
         <v>33</v>
       </c>
-      <c r="R111" t="inlineStr"/>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
       <c r="U111" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9192,7 +8471,7 @@
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>探査機パック</t>
+          <t>探测器包</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -9215,7 +8494,6 @@
           <t>{520=20;962=2;rmb=500}</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr">
         <is>
           <t>111</t>
@@ -9226,18 +8504,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
         <v>1</v>
       </c>
       <c r="P112" t="n">
         <v>33</v>
       </c>
-      <c r="R112" t="inlineStr"/>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
       <c r="U112" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9267,7 +8539,7 @@
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>探査機パック</t>
+          <t>探测器包</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -9290,7 +8562,6 @@
           <t>{520=50;963=2;rmb=2000}</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr">
         <is>
           <t>113</t>
@@ -9301,18 +8572,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
         <v>1</v>
       </c>
       <c r="P113" t="n">
         <v>33</v>
       </c>
-      <c r="R113" t="inlineStr"/>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
       <c r="U113" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9346,7 +8611,7 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>潜能パック</t>
+          <t>潜能包</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -9369,7 +8634,6 @@
           <t>{rmb=980;850=800;851=400}</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
         <v>108</v>
       </c>
@@ -9378,18 +8642,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="O115" t="n">
         <v>1</v>
       </c>
       <c r="P115" t="n">
         <v>45</v>
       </c>
-      <c r="R115" t="inlineStr"/>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
       <c r="U115" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9419,7 +8677,7 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>潜能パック</t>
+          <t>潜能包</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -9442,7 +8700,6 @@
           <t>{rmb=1980;850=1600;851=800}</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr">
         <is>
           <t>111</t>
@@ -9453,18 +8710,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
       <c r="O116" t="n">
         <v>1</v>
       </c>
       <c r="P116" t="n">
         <v>45</v>
       </c>
-      <c r="R116" t="inlineStr"/>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
       <c r="U116" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9494,7 +8745,7 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>潜能パック</t>
+          <t>潜能包</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -9517,7 +8768,6 @@
           <t>{rmb=3280;850=2400;851=1200}</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr">
         <is>
           <t>112</t>
@@ -9528,18 +8778,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
       <c r="O117" t="n">
         <v>1</v>
       </c>
       <c r="P117" t="n">
         <v>45</v>
       </c>
-      <c r="R117" t="inlineStr"/>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9573,7 +8817,7 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>ルーンパック</t>
+          <t>符文包</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9604,18 +8848,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
         <v>1</v>
       </c>
       <c r="P119" t="n">
         <v>66</v>
       </c>
-      <c r="R119" t="inlineStr"/>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9645,7 +8883,7 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>ルーンパック</t>
+          <t>符文包</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9668,7 +8906,6 @@
           <t>{531=2;529=100;rmb=120}</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
         <v>102</v>
       </c>
@@ -9677,18 +8914,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
       <c r="O120" t="n">
         <v>1</v>
       </c>
       <c r="P120" t="n">
         <v>66</v>
       </c>
-      <c r="R120" t="inlineStr"/>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9718,7 +8949,7 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>ルーンパック</t>
+          <t>符文包</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -9741,7 +8972,6 @@
           <t>{531=10;992=1;rmb=200}</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
       <c r="J121" t="n">
         <v>106</v>
       </c>
@@ -9750,18 +8980,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="O121" t="n">
         <v>1</v>
       </c>
       <c r="P121" t="n">
         <v>66</v>
       </c>
-      <c r="R121" t="inlineStr"/>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
       <c r="U121" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9791,22 +9015,19 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>ルーンパック</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr"/>
+          <t>符文包</t>
+        </is>
+      </c>
       <c r="F122" t="inlineStr">
         <is>
           <t>Rune Pack</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
       <c r="H122" s="3" t="inlineStr">
         <is>
           <t>{531=30;993=2;rmb=500}</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr"/>
       <c r="J122" t="inlineStr">
         <is>
           <t>111</t>
@@ -9817,18 +9038,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="O122" t="n">
         <v>1</v>
       </c>
       <c r="P122" t="n">
         <v>66</v>
       </c>
-      <c r="R122" t="inlineStr"/>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
       <c r="U122" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -9858,7 +9073,7 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>ルーンパック</t>
+          <t>符文包</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9916,7 +9131,7 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>ルーンパック</t>
+          <t>符文包</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9975,7 +9190,7 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>チップパック</t>
+          <t>芯片组</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -10006,18 +9221,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="O126" t="n">
         <v>1</v>
       </c>
       <c r="P126" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="R126" t="inlineStr"/>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
       <c r="U126" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -10045,7 +9254,7 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>チップパック</t>
+          <t>芯片组</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -10068,7 +9277,6 @@
           <t>{531=2;529=100;rmb=120}</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
       <c r="J127" t="n">
         <v>102</v>
       </c>
@@ -10077,18 +9285,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
       <c r="O127" t="n">
         <v>1</v>
       </c>
       <c r="P127" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="R127" t="inlineStr"/>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
       <c r="U127" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -10116,7 +9318,7 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>チップパック</t>
+          <t>芯片组</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -10139,7 +9341,6 @@
           <t>{531=10;992=1;rmb=200}</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr"/>
       <c r="J128" t="n">
         <v>106</v>
       </c>
@@ -10148,18 +9349,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
         <v>1</v>
       </c>
       <c r="P128" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="R128" t="inlineStr"/>
-      <c r="S128" t="inlineStr"/>
-      <c r="T128" t="inlineStr"/>
       <c r="U128" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -10187,22 +9382,19 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>チップパック</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr"/>
+          <t>芯片组</t>
+        </is>
+      </c>
       <c r="F129" t="inlineStr">
         <is>
           <t>Chip Pack</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
       <c r="H129" s="3" t="inlineStr">
         <is>
           <t>{531=30;993=2;rmb=500}</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr">
         <is>
           <t>111</t>
@@ -10213,18 +9405,12 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
         <v>1</v>
       </c>
       <c r="P129" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="R129" t="inlineStr"/>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr"/>
       <c r="U129" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb_djlb.png</t>
@@ -10252,7 +9438,7 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>チップパック</t>
+          <t>芯片组</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -10308,7 +9494,7 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>チップパック</t>
+          <t>芯片组</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -10367,7 +9553,7 @@
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -10390,7 +9576,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr">
         <is>
           <t>113</t>
@@ -10401,9 +9586,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr">
         <is>
           <t>3</t>
@@ -10419,9 +9601,6 @@
           <t>1971</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr"/>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
       <c r="U133" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -10451,7 +9630,7 @@
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -10474,7 +9653,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr">
         <is>
           <t>113</t>
@@ -10485,9 +9663,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr">
         <is>
           <t>3</t>
@@ -10503,9 +9678,6 @@
           <t>1271</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr"/>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
       <c r="U134" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -10535,7 +9707,7 @@
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -10558,7 +9730,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr">
         <is>
           <t>113</t>
@@ -10569,9 +9740,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr">
         <is>
           <t>3</t>
@@ -10587,9 +9755,6 @@
           <t>3631</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr"/>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr"/>
       <c r="U135" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -10619,7 +9784,7 @@
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -10642,7 +9807,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr">
         <is>
           <t>113</t>
@@ -10653,9 +9817,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr">
         <is>
           <t>3</t>
@@ -10671,9 +9832,6 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="R136" t="inlineStr"/>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
       <c r="U136" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -10703,7 +9861,7 @@
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -10726,7 +9884,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr">
         <is>
           <t>113</t>
@@ -10737,9 +9894,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>3</t>
@@ -10755,9 +9909,6 @@
           <t>1961</t>
         </is>
       </c>
-      <c r="R137" t="inlineStr"/>
-      <c r="S137" t="inlineStr"/>
-      <c r="T137" t="inlineStr"/>
       <c r="U137" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -10787,7 +9938,7 @@
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -10810,7 +9961,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
       <c r="J138" t="inlineStr">
         <is>
           <t>113</t>
@@ -10821,9 +9971,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>3</t>
@@ -10839,9 +9986,6 @@
           <t>2431</t>
         </is>
       </c>
-      <c r="R138" t="inlineStr"/>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
       <c r="U138" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -10871,7 +10015,7 @@
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -10894,7 +10038,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr">
         <is>
           <t>113</t>
@@ -10905,9 +10048,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>3</t>
@@ -10923,9 +10063,6 @@
           <t>2381</t>
         </is>
       </c>
-      <c r="R139" t="inlineStr"/>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -10955,7 +10092,7 @@
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -10978,7 +10115,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr">
         <is>
           <t>113</t>
@@ -10989,9 +10125,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
           <t>3</t>
@@ -11007,9 +10140,6 @@
           <t>2351</t>
         </is>
       </c>
-      <c r="R140" t="inlineStr"/>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr"/>
       <c r="U140" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11039,7 +10169,7 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -11062,7 +10192,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr">
         <is>
           <t>113</t>
@@ -11073,9 +10202,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr">
         <is>
           <t>3</t>
@@ -11091,9 +10217,6 @@
           <t>2361</t>
         </is>
       </c>
-      <c r="R141" t="inlineStr"/>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
       <c r="U141" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11123,7 +10246,7 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -11146,7 +10269,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr">
         <is>
           <t>113</t>
@@ -11157,9 +10279,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="O142" t="inlineStr">
         <is>
           <t>3</t>
@@ -11175,9 +10294,6 @@
           <t>2391</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr"/>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr"/>
       <c r="U142" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11207,7 +10323,7 @@
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -11230,7 +10346,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr">
         <is>
           <t>113</t>
@@ -11241,9 +10356,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr">
         <is>
           <t>3</t>
@@ -11259,9 +10371,6 @@
           <t>2441</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr"/>
-      <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr"/>
       <c r="U143" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11291,7 +10400,7 @@
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -11314,7 +10423,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr">
         <is>
           <t>113</t>
@@ -11325,9 +10433,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr">
         <is>
           <t>3</t>
@@ -11343,9 +10448,6 @@
           <t>3641</t>
         </is>
       </c>
-      <c r="R144" t="inlineStr"/>
-      <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
       <c r="U144" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11375,7 +10477,7 @@
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -11398,7 +10500,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr">
         <is>
           <t>113</t>
@@ -11409,9 +10510,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="O145" t="inlineStr">
         <is>
           <t>3</t>
@@ -11427,9 +10525,6 @@
           <t>3211</t>
         </is>
       </c>
-      <c r="R145" t="inlineStr"/>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr"/>
       <c r="U145" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11459,7 +10554,7 @@
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -11482,7 +10577,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
       <c r="J146" t="inlineStr">
         <is>
           <t>113</t>
@@ -11493,9 +10587,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr">
         <is>
           <t>3</t>
@@ -11511,9 +10602,6 @@
           <t>3221</t>
         </is>
       </c>
-      <c r="R146" t="inlineStr"/>
-      <c r="S146" t="inlineStr"/>
-      <c r="T146" t="inlineStr"/>
       <c r="U146" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11543,7 +10631,7 @@
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -11566,7 +10654,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
       <c r="J147" t="inlineStr">
         <is>
           <t>113</t>
@@ -11577,9 +10664,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr">
         <is>
           <t>3</t>
@@ -11595,9 +10679,6 @@
           <t>3241</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr"/>
-      <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11627,7 +10708,7 @@
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -11650,7 +10731,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr">
         <is>
           <t>113</t>
@@ -11661,9 +10741,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr">
         <is>
           <t>3</t>
@@ -11679,9 +10756,6 @@
           <t>3261</t>
         </is>
       </c>
-      <c r="R148" t="inlineStr"/>
-      <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr"/>
       <c r="U148" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11711,7 +10785,7 @@
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -11734,7 +10808,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
       <c r="J149" t="inlineStr">
         <is>
           <t>113</t>
@@ -11745,9 +10818,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr">
         <is>
           <t>3</t>
@@ -11763,9 +10833,6 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="R149" t="inlineStr"/>
-      <c r="S149" t="inlineStr"/>
-      <c r="T149" t="inlineStr"/>
       <c r="U149" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11795,7 +10862,7 @@
       </c>
       <c r="D150" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -11818,7 +10885,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr">
         <is>
           <t>113</t>
@@ -11829,9 +10895,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>3</t>
@@ -11847,9 +10910,6 @@
           <t>4171</t>
         </is>
       </c>
-      <c r="R150" t="inlineStr"/>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
       <c r="U150" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11879,7 +10939,7 @@
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -11902,7 +10962,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr">
         <is>
           <t>113</t>
@@ -11913,9 +10972,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr">
         <is>
           <t>3</t>
@@ -11931,9 +10987,6 @@
           <t>3611</t>
         </is>
       </c>
-      <c r="R151" t="inlineStr"/>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
       <c r="U151" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -11963,7 +11016,7 @@
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -11986,7 +11039,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
       <c r="J152" t="inlineStr">
         <is>
           <t>113</t>
@@ -11997,9 +11049,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr">
         <is>
           <t>3</t>
@@ -12015,9 +11064,6 @@
           <t>1281</t>
         </is>
       </c>
-      <c r="R152" t="inlineStr"/>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -12047,7 +11093,7 @@
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -12070,7 +11116,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr">
         <is>
           <t>113</t>
@@ -12081,9 +11126,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
           <t>3</t>
@@ -12099,9 +11141,6 @@
           <t>3271</t>
         </is>
       </c>
-      <c r="R153" t="inlineStr"/>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
       <c r="U153" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -12131,7 +11170,7 @@
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -12154,7 +11193,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr">
         <is>
           <t>113</t>
@@ -12165,9 +11203,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
           <t>3</t>
@@ -12183,9 +11218,6 @@
           <t>3601</t>
         </is>
       </c>
-      <c r="R154" t="inlineStr"/>
-      <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr"/>
       <c r="U154" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -12215,7 +11247,7 @@
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>育成パック</t>
+          <t>育成包</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -12238,7 +11270,6 @@
           <t>{card={id=761};rmb=6480;19=100;604=100;452=300}</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
           <t>113</t>
@@ -12249,9 +11280,6 @@
           <t>1080</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr">
         <is>
           <t>3</t>
@@ -12267,9 +11295,6 @@
           <t>4161</t>
         </is>
       </c>
-      <c r="R155" t="inlineStr"/>
-      <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr"/>
       <c r="U155" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -12281,30 +11306,8 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" t="inlineStr"/>
-      <c r="B156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr"/>
-      <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr"/>
-      <c r="U156" t="inlineStr"/>
-      <c r="V156" t="inlineStr"/>
-    </row>
+    <row r="156"/>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
           <t>21001</t>
@@ -12340,7 +11343,6 @@
           <t>{rmb=2280;6212=1;519=10}</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
           <t>111</t>
@@ -12351,19 +11353,11 @@
           <t>4320</t>
         </is>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
       <c r="O157" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
-      <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
       <c r="U157" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -12376,7 +11370,6 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
           <t>21001</t>
@@ -12412,7 +11405,6 @@
           <t>{rmb=6880;937=1;527=20;19=50}</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
           <t>113</t>
@@ -12423,19 +11415,11 @@
           <t>4320</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
-      <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr"/>
       <c r="U158" t="inlineStr">
         <is>
           <t>activity/limit_buy_gift/bg_xslb.png</t>
@@ -12448,176 +11432,37 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
-      <c r="B159" t="inlineStr"/>
       <c r="C159" s="4" t="inlineStr"/>
       <c r="D159" s="4" t="n"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr"/>
-      <c r="U159" t="inlineStr"/>
-      <c r="V159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
-      <c r="B160" t="inlineStr"/>
       <c r="C160" s="4" t="inlineStr"/>
       <c r="D160" s="4" t="n"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr"/>
-      <c r="U160" t="inlineStr"/>
-      <c r="V160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
-      <c r="B161" t="inlineStr"/>
       <c r="C161" s="4" t="inlineStr"/>
       <c r="D161" s="4" t="n"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
-      <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
-      <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr"/>
-      <c r="U161" t="inlineStr"/>
-      <c r="V161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
-      <c r="B162" t="inlineStr"/>
       <c r="C162" s="4" t="inlineStr"/>
       <c r="D162" s="4" t="n"/>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr"/>
-      <c r="S162" t="inlineStr"/>
-      <c r="T162" t="inlineStr"/>
-      <c r="U162" t="inlineStr"/>
-      <c r="V162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
-      <c r="B163" t="inlineStr"/>
       <c r="C163" s="4" t="inlineStr"/>
       <c r="D163" s="4" t="n"/>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
-      <c r="I163" t="inlineStr"/>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="inlineStr"/>
-      <c r="S163" t="inlineStr"/>
-      <c r="T163" t="inlineStr"/>
-      <c r="U163" t="inlineStr"/>
-      <c r="V163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr"/>
       <c r="C164" s="4" t="inlineStr"/>
       <c r="D164" s="4" t="n"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr"/>
-      <c r="U164" t="inlineStr"/>
-      <c r="V164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr"/>
       <c r="C165" s="4" t="inlineStr"/>
       <c r="D165" s="4" t="n"/>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
-      <c r="I165" t="inlineStr"/>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
           <t>4320</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr"/>
-      <c r="U165" t="inlineStr"/>
-      <c r="V165" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
